--- a/auto-hub-reactive-agency/src/test/resources/file/Cars.xlsx
+++ b/auto-hub-reactive-agency/src/test/resources/file/Cars.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\swift-wheels-hub-reactive\swift-wheels-hub-reactive-agency\src\test\resources\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\auto-hub-reactive\auto-hub-reactive-agency\src\test\resources\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49D47ED-492F-4D34-8559-37E275FC39FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F30B90-AE1E-4DA0-B219-9C0760EA9BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>YEAR OF PRODUCTION</t>
   </si>
   <si>
-    <t xml:space="preserve"> ORIGINAL BRANCH ID</t>
-  </si>
-  <si>
     <t>ACTUAL BRANCH ID</t>
   </si>
   <si>
@@ -76,6 +73,9 @@
   </si>
   <si>
     <t>65072051d5d4531e66a0c00a</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INITIAL BRANCH ID</t>
   </si>
 </sst>
 </file>
@@ -496,45 +496,45 @@
         <v>3</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="168" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="D2" s="2">
         <v>2010</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
         <v>270000</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2">
         <v>500</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
